--- a/data/trans_camb/P15-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P15-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 4,33</t>
+          <t>-3,2; 4,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,98</t>
+          <t>-5,18; 1,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,49</t>
+          <t>-5,65; 0,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 4,29</t>
+          <t>-3,34; 4,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 4,18</t>
+          <t>-2,81; 4,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,33</t>
+          <t>-3,39; 2,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,07</t>
+          <t>-1,99; 3,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,28</t>
+          <t>-3,49; 1,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,69</t>
+          <t>-3,64; 0,81</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 75,98</t>
+          <t>-36,43; 78,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,05; 20,03</t>
+          <t>-59,22; 29,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,27; 10,75</t>
+          <t>-62,0; 11,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 124,39</t>
+          <t>-50,23; 129,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 130,33</t>
+          <t>-40,99; 147,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,59; 71,61</t>
+          <t>-44,92; 87,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,46; 58,32</t>
+          <t>-26,34; 68,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,92; 26,38</t>
+          <t>-45,88; 28,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,78; 13,57</t>
+          <t>-45,75; 17,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 4,18</t>
+          <t>-3,29; 4,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 0,95</t>
+          <t>-6,57; 0,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 2,31</t>
+          <t>-5,35; 2,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,82</t>
+          <t>1,41; 8,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 6,45</t>
+          <t>-0,28; 6,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 5,32</t>
+          <t>-0,1; 5,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,27</t>
+          <t>0,32; 5,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,57</t>
+          <t>-2,2; 2,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,0</t>
+          <t>-1,6; 2,95</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 84,07</t>
+          <t>-36,58; 88,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,34; 20,14</t>
+          <t>-68,64; 15,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,31; 52,71</t>
+          <t>-60,46; 42,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,71; 517,56</t>
+          <t>23,75; 416,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 341,59</t>
+          <t>-15,77; 299,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 287,66</t>
+          <t>-4,77; 304,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 135,17</t>
+          <t>3,34; 133,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 70,79</t>
+          <t>-35,4; 64,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 76,88</t>
+          <t>-26,2; 74,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,89</t>
+          <t>-3,13; 4,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 0,46</t>
+          <t>-6,0; 0,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 0,68</t>
+          <t>-9,83; 0,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 6,69</t>
+          <t>-1,03; 7,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 7,83</t>
+          <t>-0,97; 8,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 8,0</t>
+          <t>0,15; 8,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,07</t>
+          <t>-1,85; 3,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,39</t>
+          <t>-4,41; 1,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 1,57</t>
+          <t>-6,47; 1,0</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 52,16</t>
+          <t>-29,46; 56,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,27; 8,42</t>
+          <t>-58,64; 2,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,76; 6,58</t>
+          <t>-81,3; 3,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 572,71</t>
+          <t>-32,46; 649,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,64; 682,49</t>
+          <t>-43,1; 695,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 606,2</t>
+          <t>-9,7; 577,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 68,88</t>
+          <t>-20,94; 64,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 22,99</t>
+          <t>-48,49; 18,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,03; 22,15</t>
+          <t>-69,48; 14,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,68</t>
+          <t>-0,77; 3,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,15</t>
+          <t>-3,5; 0,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,0</t>
+          <t>-2,46; 1,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,77</t>
+          <t>-2,25; 2,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,77</t>
+          <t>-3,67; 0,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,48</t>
+          <t>-4,28; 1,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,68</t>
+          <t>-0,61; 2,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; -0,15</t>
+          <t>-3,03; -0,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,93</t>
+          <t>-2,89; 0,86</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 62,67</t>
+          <t>-9,7; 62,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 2,83</t>
+          <t>-44,92; 4,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 35,29</t>
+          <t>-31,31; 27,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 56,04</t>
+          <t>-31,41; 58,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 17,32</t>
+          <t>-49,7; 19,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 29,01</t>
+          <t>-58,06; 26,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 45,74</t>
+          <t>-8,43; 46,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,35; -2,65</t>
+          <t>-40,69; -1,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 14,99</t>
+          <t>-38,82; 14,32</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 5,19</t>
+          <t>-1,54; 5,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,92</t>
+          <t>-2,89; 3,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,17</t>
+          <t>-1,44; 6,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,01</t>
+          <t>-1,64; 4,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,49</t>
+          <t>-3,77; 1,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,34</t>
+          <t>-3,04; 2,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,7</t>
+          <t>-0,77; 3,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,7</t>
+          <t>-2,41; 1,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,96</t>
+          <t>-1,59; 2,92</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 138,59</t>
+          <t>-21,25; 141,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 98,86</t>
+          <t>-35,5; 83,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 151,47</t>
+          <t>-19,77; 156,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 81,69</t>
+          <t>-21,82; 81,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,5; 33,02</t>
+          <t>-46,26; 33,41</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-39,39; 47,06</t>
+          <t>-37,1; 44,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 72,63</t>
+          <t>-10,3; 75,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 34,79</t>
+          <t>-31,64; 33,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 57,11</t>
+          <t>-22,37; 59,1</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 5,5</t>
+          <t>-4,68; 5,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 5,93</t>
+          <t>-4,93; 5,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 1,5</t>
+          <t>-9,7; 2,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,21</t>
+          <t>1,13; 5,39</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>-1,53; 2,57</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-0,83; 3,22</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0,59; 4,33</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>-1,26; 2,43</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-0,75; 3,37</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0,64; 4,57</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-1,13; 2,54</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,32</t>
+          <t>-1,89; 1,99</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 72,78</t>
+          <t>-38,64; 74,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 81,3</t>
+          <t>-41,3; 76,15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-85,63; 20,86</t>
+          <t>-82,61; 55,08</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17,02; 124,47</t>
+          <t>17,38; 124,98</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 58,42</t>
+          <t>-26,31; 60,74</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 78,86</t>
+          <t>-15,11; 75,51</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,31; 86,87</t>
+          <t>8,63; 83,14</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 47,73</t>
+          <t>-18,68; 48,31</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 44,44</t>
+          <t>-27,68; 38,94</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,4</t>
+          <t>-0,34; 2,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,34</t>
+          <t>-2,75; -0,36</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -0,16</t>
+          <t>-3,32; -0,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,3</t>
+          <t>0,93; 3,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,31</t>
+          <t>-0,93; 1,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,8</t>
+          <t>-0,56; 1,85</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,38</t>
+          <t>0,68; 2,44</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,18</t>
+          <t>-1,4; 0,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,48</t>
+          <t>-1,5; 0,43</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 35,27</t>
+          <t>-4,51; 33,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,34; -4,79</t>
+          <t>-34,38; -5,06</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,76; -2,24</t>
+          <t>-41,02; -3,81</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16,71; 69,39</t>
+          <t>16,54; 71,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 27,8</t>
+          <t>-16,2; 28,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 37,19</t>
+          <t>-9,98; 40,8</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,52; 41,04</t>
+          <t>10,03; 40,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,7; 3,18</t>
+          <t>-20,69; 4,49</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 8,15</t>
+          <t>-22,5; 8,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P15-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P15-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,49</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-1,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 4,48</t>
+          <t>-3,16; 4,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 1,46</t>
+          <t>-5,42; 1,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,4</t>
+          <t>-5,49; 0,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 4,34</t>
+          <t>-3,2; 4,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 4,63</t>
+          <t>-2,85; 4,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,75</t>
+          <t>-2,98; 2,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,45</t>
+          <t>-2,34; 3,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,42</t>
+          <t>-3,39; 1,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,81</t>
+          <t>-3,62; 0,6</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-34,58%</t>
+          <t>-34,86%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-23,08%</t>
+          <t>-21,96%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,43; 78,99</t>
+          <t>-34,11; 77,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 29,04</t>
+          <t>-61,45; 23,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,0; 11,35</t>
+          <t>-60,54; 19,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,23; 129,79</t>
+          <t>-47,53; 152,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 147,5</t>
+          <t>-44,73; 128,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 87,97</t>
+          <t>-42,05; 83,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 68,45</t>
+          <t>-30,7; 64,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,88; 28,03</t>
+          <t>-43,72; 31,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 17,17</t>
+          <t>-45,36; 12,62</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-1,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 4,55</t>
+          <t>-3,3; 4,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 0,69</t>
+          <t>-6,45; 0,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,11</t>
+          <t>-5,68; 1,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,64</t>
+          <t>1,16; 8,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 6,22</t>
+          <t>-0,34; 5,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,37</t>
+          <t>-0,02; 5,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,31</t>
+          <t>0,21; 5,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,58</t>
+          <t>-2,31; 2,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,95</t>
+          <t>-1,88; 2,6</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-24,1%</t>
+          <t>-24,31%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 88,39</t>
+          <t>-36,36; 89,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,64; 15,44</t>
+          <t>-68,87; 17,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,46; 42,78</t>
+          <t>-60,33; 32,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,75; 416,37</t>
+          <t>18,02; 440,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 299,41</t>
+          <t>-9,55; 310,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 304,73</t>
+          <t>-3,74; 321,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 133,0</t>
+          <t>2,91; 149,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 64,78</t>
+          <t>-36,68; 61,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 74,39</t>
+          <t>-29,13; 66,43</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,79</t>
+          <t>-0,87</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,97</t>
+          <t>0,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 4,02</t>
+          <t>-3,03; 4,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 0,23</t>
+          <t>-6,05; 0,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 0,29</t>
+          <t>-4,41; 2,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 7,17</t>
+          <t>-0,4; 7,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 8,0</t>
+          <t>-1,04; 8,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 8,03</t>
+          <t>0,05; 7,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,83</t>
+          <t>-1,83; 3,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 1,07</t>
+          <t>-3,98; 1,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 1,0</t>
+          <t>-3,02; 2,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-43,16%</t>
+          <t>-9,96%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>143,3%</t>
+          <t>129,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-26,65%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 56,41</t>
+          <t>-27,82; 61,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,64; 2,77</t>
+          <t>-56,41; 12,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,3; 3,54</t>
+          <t>-40,92; 38,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 649,67</t>
+          <t>-20,33; 750,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 695,54</t>
+          <t>-33,68; 794,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 577,93</t>
+          <t>-12,26; 546,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 64,01</t>
+          <t>-20,7; 61,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,49; 18,39</t>
+          <t>-44,99; 17,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,48; 14,39</t>
+          <t>-33,52; 48,05</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,63</t>
+          <t>-0,67; 3,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,31</t>
+          <t>-3,72; 0,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,67</t>
+          <t>-1,99; 2,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,75</t>
+          <t>-2,38; 2,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,89</t>
+          <t>-3,72; 0,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,41</t>
+          <t>-2,2; 2,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,73</t>
+          <t>-0,47; 2,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; -0,07</t>
+          <t>-2,98; -0,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,86</t>
+          <t>-1,5; 1,72</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-5,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-16,72%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-11,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 62,37</t>
+          <t>-9,42; 62,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 4,52</t>
+          <t>-46,35; 2,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 27,11</t>
+          <t>-26,7; 38,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 58,27</t>
+          <t>-31,83; 50,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 19,68</t>
+          <t>-50,53; 18,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,06; 26,02</t>
+          <t>-29,34; 53,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 46,45</t>
+          <t>-6,59; 46,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,69; -1,09</t>
+          <t>-40,43; -0,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,82; 14,32</t>
+          <t>-20,44; 30,0</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,43</t>
+          <t>-1,65; 5,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 3,61</t>
+          <t>-2,51; 3,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,38</t>
+          <t>-2,11; 4,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,05</t>
+          <t>-1,84; 3,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,63</t>
+          <t>-3,53; 1,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,25</t>
+          <t>-2,21; 2,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,76</t>
+          <t>-0,66; 3,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,69</t>
+          <t>-2,29; 1,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,92</t>
+          <t>-1,35; 2,97</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 141,11</t>
+          <t>-25,28; 133,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 83,62</t>
+          <t>-33,18; 89,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 156,0</t>
+          <t>-29,71; 123,16</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 81,91</t>
+          <t>-23,28; 72,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 33,41</t>
+          <t>-45,12; 31,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,1; 44,58</t>
+          <t>-28,29; 59,76</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 75,38</t>
+          <t>-8,93; 73,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 33,52</t>
+          <t>-30,64; 37,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 59,1</t>
+          <t>-18,57; 60,24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-4,95</t>
+          <t>-5,1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,37</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 5,3</t>
+          <t>-5,0; 4,8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 5,45</t>
+          <t>-4,65; 5,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 2,96</t>
+          <t>-9,61; 1,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,39</t>
+          <t>1,16; 5,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,57</t>
+          <t>-1,23; 2,44</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,22</t>
+          <t>-0,8; 2,75</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,33</t>
+          <t>0,67; 4,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,43</t>
+          <t>-1,13; 2,52</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,99</t>
+          <t>-2,13; 1,73</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-50,39%</t>
+          <t>-51,88%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-2,23%</t>
+          <t>-6,25%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 74,05</t>
+          <t>-39,66; 62,53</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 76,15</t>
+          <t>-39,77; 77,21</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-82,61; 55,08</t>
+          <t>-81,87; 25,84</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17,38; 124,98</t>
+          <t>19,39; 122,98</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 60,74</t>
+          <t>-21,12; 57,75</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 75,51</t>
+          <t>-14,36; 65,6</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,63; 83,14</t>
+          <t>10,66; 87,07</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 48,31</t>
+          <t>-17,6; 49,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 38,94</t>
+          <t>-32,06; 33,91</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,54</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,01</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,26</t>
+          <t>-0,5; 2,28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,36</t>
+          <t>-2,78; -0,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,32; -0,25</t>
+          <t>-2,44; 0,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,23</t>
+          <t>0,9; 3,19</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,29</t>
+          <t>-0,8; 1,34</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,85</t>
+          <t>-0,07; 2,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,44</t>
+          <t>0,72; 2,4</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,26</t>
+          <t>-1,42; 0,17</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,43</t>
+          <t>-0,87; 0,77</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-20,81%</t>
+          <t>-14,35%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-7,12%</t>
+          <t>-0,17%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 33,11</t>
+          <t>-5,9; 33,47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -5,06</t>
+          <t>-34,64; -4,88</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,02; -3,81</t>
+          <t>-30,09; 4,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16,54; 71,65</t>
+          <t>15,93; 69,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 28,0</t>
+          <t>-14,23; 28,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 40,8</t>
+          <t>-1,37; 44,58</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,03; 40,82</t>
+          <t>10,72; 41,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 4,49</t>
+          <t>-20,74; 3,11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 8,04</t>
+          <t>-12,81; 13,29</t>
         </is>
       </c>
     </row>
